--- a/wiwynn/dist/20261025_緯穎模型_v0.1.xlsx
+++ b/wiwynn/dist/20261025_緯穎模型_v0.1.xlsx
@@ -4207,7 +4207,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5396,7 +5396,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6381,7 +6381,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6561,7 +6561,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6663,7 +6663,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6786,7 +6786,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -18089,7 +18089,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -33309,7 +33309,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.xlsx</t>
     </r>
   </si>
   <si>

--- a/wiwynn/dist/20261025_緯穎模型_v0.1.xlsx
+++ b/wiwynn/dist/20261025_緯穎模型_v0.1.xlsx
@@ -4627,7 +4627,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4826,7 +4826,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4947,7 +4947,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5068,7 +5068,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5189,7 +5189,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5310,7 +5310,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5542,7 +5542,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -33271,7 +33271,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
